--- a/OUTPUT/direct_Q9ZFA4_Rhodobacter_sphaeroides_2_4_1.xlsx
+++ b/OUTPUT/direct_Q9ZFA4_Rhodobacter_sphaeroides_2_4_1.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.004</v>
+        <v>0.004198320671731308</v>
       </c>
     </row>
   </sheetData>
